--- a/Cubo_Sitelo.xlsx
+++ b/Cubo_Sitelo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerald Rocha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerald Rocha\Documents\GitHub\Mapa TN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41EF58A-480D-49B2-96E5-474649DB51CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3648E3E0-7A0C-4C5C-A22E-F472ED2D553F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B2C8BF5B-C28F-4A4B-B360-42E661C3BE08}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
   <si>
     <t>PC</t>
   </si>
@@ -39,15 +39,6 @@
     <t>OF</t>
   </si>
   <si>
-    <t>AMPM03</t>
-  </si>
-  <si>
-    <t>AMPM02</t>
-  </si>
-  <si>
-    <t>AMPM01</t>
-  </si>
-  <si>
     <t>Categorias</t>
   </si>
   <si>
@@ -63,63 +54,21 @@
     <t>Tipo</t>
   </si>
   <si>
-    <t>Pto 4 - La Campana</t>
-  </si>
-  <si>
-    <t>Pto 2 - Santa Helena</t>
-  </si>
-  <si>
-    <t>Pto 7 - Blvr Los Herores</t>
-  </si>
-  <si>
-    <t>Pto 16 - Parque San Martin</t>
-  </si>
-  <si>
-    <t>Pto 25 - Comex Calle poniente</t>
-  </si>
-  <si>
-    <t>Pto 32 - Farmacias Uno</t>
-  </si>
-  <si>
     <t>SA</t>
   </si>
   <si>
-    <t>Pto 34 - CC Las Acacias</t>
-  </si>
-  <si>
-    <t>Pto 42- Plaza Orion</t>
-  </si>
-  <si>
     <t>Centro Historico</t>
   </si>
   <si>
     <t>Link</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/Restaurante+Kreef+%E2%80%A2+Santa+Elena/@13.6711703,-89.2551685,20.24z/data=!4m9!1m2!2m1!1sBulevar+Santa+Elena+San+Salvador+CP,+1101,+El+Salvador!3m5!1s0x8f632e2fec9a41f7:0x624adb154d2cfc6d!8m2!3d13.6713362!4d-89.2549542!16s%2Fg%2F1hc3bkwx6?entry=ttu&amp;g_ep=EgoyMDI2MDQyOS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Bom+Bom+%C2%B7+Salvador+del+Mundo/@13.7014345,-89.2236391,20.65z/data=!4m10!1m2!2m1!1sAlameda+Roosevelt+%26,+PQ2G%2BJMG,+65+Avenida+Nte.,+San+Salvador,+El+Salvador!3m6!1s0x8f63310042d37921:0x9fd598f8eb212dc4!8m2!3d13.7015545!4d-89.2233004!15sCklBbGFtZWRhIFJvb3NldmVsdCAmLCBQUTJHK0pNRywgNjUgQXZlbmlkYSBOdGUuLCBTYW4gU2FsdmFkb3IsIEVsIFNhbHZhZG9yWkYiRGFsYW1lZGEgcm9vc2V2ZWx0ICYgcHEyZyBqbWcgNjUgYXZlbmlkYSBudGUgc2FuIHNhbHZhZG9yIGVsIHNhbHZhZG9ykgEJY2FrZV9zaG9wmgFEQ2k5RFFVbFJRVU52WkVOb2RIbGpSamx2VDIwMU0xWnFaSHBhTTI5NVlXcEdjbE5YUm10T01VNUpUbTVhZUdOdVl4QULgAQD6AQQIABBG!16s%2Fg%2F11n9ttxnyb?entry=ttu&amp;g_ep=EgoyMDI2MDQyOS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Rosy+Avril+El+Salvador/@13.7081581,-89.2123075,20.24z/data=!4m9!1m2!2m1!1sMetrocentro,+San+Salvador,+El+Salvador+%2B503+6031+6654!3m5!1s0x8f6331372297885d:0x4f3bc5008915c61!8m2!3d13.7079147!4d-89.2119485!16s%2Fg%2F11rc1_lmnc?entry=ttu&amp;g_ep=EgoyMDI2MDQyOS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/place/Little+Caesars+%E2%80%A2+Santa+Tecla/@13.6730847,-89.2863212,19z/data=!4m10!1m2!2m1!1sCarretera+Panamericana+frente+a+parque+San+Mart%C3%ADn,+Santa+Tecla,+El+Salvador!3m6!1s0x8f632ef887cfaff7:0xee3c9657cc1dad8b!8m2!3d13.6729273!4d-89.2852676!15sCkxDYXJyZXRlcmEgUGFuYW1lcmljYW5hIGZyZW50ZSBhIHBhcnF1ZSBTYW4gTWFydMOtbiwgU2FudGEgVGVjbGEsIEVsIFNhbHZhZG9yWkwiSmNhcnJldGVyYSBwYW5hbWVyaWNhbmEgZnJlbnRlIGEgcGFycXVlIHNhbiBtYXJ0w61uIHNhbnRhIHRlY2xhIGVsIHNhbHZhZG9ykgENcGl6emF0YWtlYXdheZoBRENpOURRVWxSUVVOdlpFTm9kSGxqUmpsdlQya3hlVnByVG1sa01HUkVVVEpLVWt4VlJYaGxWMFY2WWtkU05WVnNSUkFC4AEA-gEECAAQRw!16s%2Fg%2F11b7fx99x1?entry=ttu&amp;g_ep=EgoyMDI2MDQyOS4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/Reveuse,+Equipos+y+m%C3%A1s/@13.7135826,-89.1920429,19.04z/data=!4m10!1m2!2m1!1sy+3,+Edificio+Marvel+local,+29+Calle+Poniente,+San+Salvador,+El+Salvador!3m6!1s0x8f6337e6bdc488b1:0x3acf57f174f02592!8m2!3d13.7134475!4d-89.1917686!15sCkh5IDMsIEVkaWZpY2lvIE1hcnZlbCBsb2NhbCwgMjkgQ2FsbGUgUG9uaWVudGUsIFNhbiBTYWx2YWRvciwgRWwgU2FsdmFkb3KSAQ9mdXJuaXR1cmVfc3RvcmXgAQA!16s%2Fg%2F11xnvm0fzw?entry=ttu&amp;g_ep=EgoyMDI2MDQyOS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Taquer%C3%ADa+Los+H%C3%A9roes+503+%7C+Sucursal+San+Luis/@13.7151931,-89.211952,19.55z/data=!4m6!3m5!1s0x8f633b3ffc44c6ed:0xedd0a0ac751bb5ac!8m2!3d13.715139!4d-89.2116457!16s%2Fg%2F11l1qcycgf?entry=ttu&amp;g_ep=EgoyMDI2MDQyOS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/place/Centro+Comercial+Las+Acacias/@13.67627,-89.2271416,20.06z/data=!4m14!1m7!3m6!1s0x8f6331b5e671cef7:0x6d1c1ba608a84089!2sCentro+Comercial+Las+Acacias!8m2!3d13.6762059!4d-89.2270071!16s%2Fg%2F11c0rqvxh4!3m5!1s0x8f6331b5e671cef7:0x6d1c1ba608a84089!8m2!3d13.6762059!4d-89.2270071!16s%2Fg%2F11c0rqvxh4?entry=ttu&amp;g_ep=EgoyMDI2MDQyOS4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/El+Chory/@13.702475,-89.2360347,20.49z/data=!4m15!1m8!3m7!1s0x8f63303d101d661f:0x7db010d52f2bcc07!2sP.%C2%BA+Gral.+Escal%C3%B3n+4018,+San+Salvador!3b1!8m2!3d13.7026237!4d-89.2354067!16s%2Fg%2F11h6df108t!3m5!1s0x8f63316161beeef3:0xa3b2dc9c44966776!8m2!3d13.7024539!4d-89.235608!16s%2Fg%2F11v5wc6ddn?entry=ttu&amp;g_ep=EgoyMDI2MDQyOS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/place/Parada+Salandra/@13.6996528,-89.1896825,21z/data=!4m14!1m7!3m6!1s0x8f6330ea1449336b:0xb403b4c9c1bf71db!2sBAC+Credomatic+%7C+Centro!8m2!3d13.6998094!4d-89.1905811!16s%2Fg%2F11f13g5ldd!3m5!1s0x8f6330ebb60115cf:0xf259a3590bff6bdd!8m2!3d13.6996954!4d-89.1895169!16s%2Fg%2F1hjh1rkpm?entry=ttu&amp;g_ep=EgoyMDI2MDQyOS4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
   <si>
@@ -138,12 +87,6 @@
     <t>Zona Rosa</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/Tienda+de+Mascotas+Goldpets/@13.6753528,-89.2884597,19.98z/data=!4m6!3m5!1s0x8f632fcb82d13f7b:0xd97da6454f957670!8m2!3d13.6754339!4d-89.2878205!16s%2Fg%2F11rmwcb435?entry=ttu&amp;g_ep=EgoyMDI2MDQyOS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
-    <t>Paseo el Carmen</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/@13.7001356,-89.1526645,3a,81.7y,177.63h,90.03t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgIDT9v7MLw!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53avMHVydIHYJtg4Yvps2wTpkV6aW2KG3ECvtH1HJwJKEvOOC1Wj4kStQNqYN6WwM3et_Q9NJGkuSw-vQ_T6uMkvd0q7njLGYNLEmPhL3vxR-LN9XTXyajt2IzsRS4vtSFEBfro%3Dw900-h600-k-no-pi-0.03261316815279258-ya73.37491875469924-ro0-fo100!7i8000!8i4000?entry=ttu&amp;g_ep=EgoyMDI2MDQyOS4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
   <si>
@@ -183,56 +126,149 @@
     <t>Link PDF Sitelo</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1ykcO4-oqoWMhQklm81gGhFHngof9PThT/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/18Ca_WI-OP8r2bqUoUvdPoZtizObtSVwD/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Wq9okMGiiQ_DDw2MVniTKx3xWVHenCq9/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1MBu6jToIZ35t3JKQNNOs-qExgL9CzCpv/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1tNh-Oc61OjOHfdFC8wUFLaNUhB-lvJZl/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FUQmUBtGttqfQqby4lEAY6A_pgBaCjpN/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1PgchX03nK4dYJzcCoMcd_aW9Y2-aoFJe/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1JLzkbGBG3hT9cd03Gucxv1XKcSwylEl9/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Nstvrhw6u5dvdsBKqVks6_jNEX9ArgUi/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1D5Q93awaBNxb3t0ix0aQa5AN_ZA8zbDV/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1TcJxaBKO2D4imak26MmgjPh2CKKjpuoB/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/10hYzxd55NnRVdIg7klG2C_6mltZO2B1I/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1UCzlw1uAp6TGKSbxyzSS0RBe8uZwFtM5/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1tBvWkCdTf5aFyyTuVBfGol8BdK0k5LpE/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1uGcoXO-hbzoVtkn0keVL-0NeVad9q_GJ/view?usp=drive_link</t>
+    <t>https://www.google.com/maps/place/Restaurante+Kreef+%E2%80%A2+Santa+Elena/@13.6680113,-89.2564638,3a,75y,133.17h,97.82t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgICx3Ze-TA!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53ahnY0LpyIi0bKPdnJo9epDs25_23h4wz7q3PVyHmpj9MkrZiskHCkQDmgNVTzM9ACecXxMY1WVewhOoFgM2DS2agZpC_5e5dMT0z7FLK5w9rEAFZw1bnWD540wsbfDCiL-mdF%3Dw900-h600-k-no-pi-7.824501826098839-ya76.81318855877765-ro0-fo100!7i3840!8i1920!4m10!1m2!2m1!1sBulevar+Santa+Elena+San+Salvador+CP,+1101,+El+Salvador!3m6!1s0x8f632e2fec9a41f7:0x624adb154d2cfc6d!8m2!3d13.6713362!4d-89.2549542!10e5!16s%2Fg%2F1hc3bkwx6?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Link Street View</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Farmacia+San+Nicol%C3%A1s+%C2%B7+La+Campana/@13.7008479,-89.2223021,21z/data=!4m9!1m2!2m1!1sAlameda+Roosevelt+%26,+PQ2G%2BJMG,+65+Avenida+Nte.,+San+Salvador,+El+Salvador!3m5!1s0x8f633043c65255ab:0x313f1cbb226a21fe!8m2!3d13.7007732!4d-89.2219364!16s%2Fg%2F1q62pxp1f?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/Alameda+Roosevelt+%26,+PQ2G%2BJMG,+65+Avenida+Nte.,+San+Salvador,+El+Salvador/@13.6680002,-89.2563682,21z?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Farmacia+San+Nicol%C3%A1s+%C2%B7+La+Campana/@13.7009911,-89.222111,3a,75y,176.05h,90t/data=!3m8!1e1!3m6!1sCIABIhCSCJd4AzPugqu9Bz6jFzQ1!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53SbgwpckHQueuHTaUgJoULGTw2tFtGJz-PxoqN2o88srZQ04xIA4uBwpEMtkNh_nUy1me8OWswwQ_tl8-NNojCqOIlg6IBhVGQpgC8RYZ-IIipZwj_70Tb5x-aAbA49ZK42ryIkUHJ1hE%3Dw900-h600-k-no-pi0-ya48.95556120827659-ro0-fo100!7i7680!8i3840!4m9!1m2!2m1!1sAlameda+Roosevelt+%26,+PQ2G%2BJMG,+65+Avenida+Nte.,+San+Salvador,+El+Salvador!3m5!1s0x8f633043c65255ab:0x313f1cbb226a21fe!8m2!3d13.7007732!4d-89.2219364!16s%2Fg%2F1q62pxp1f?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Little+Caesars+%E2%80%A2+Santa+Tecla/@13.6730763,-89.2850389,3a,75y,180.9h,77.33t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgICb2vzXrAE!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf50b1uM_ODtfDhFXtO1sWnEz6_jBGLnfvM4CjVafDYSmGAMvW5B8dkawjYnxdA2c3iP8RlZmXTrEXwWaXRFBlRcCdC2Wt2tJHYP64UExNDiqPNM5jIMatUDqx_Nt0dp8iS0YqpbvOg%3Dw900-h600-k-no-pi12.672631266104702-ya269.4800209230051-ro0-fo100!7i8000!8i4000!4m10!1m2!2m1!1sCarretera+Panamericana+frente+a+parque+San+Mart%C3%ADn,+Santa+Tecla,+El+Salvador!3m6!1s0x8f632ef887cfaff7:0xee3c9657cc1dad8b!8m2!3d13.6729273!4d-89.2852676!15sCkxDYXJyZXRlcmEgUGFuYW1lcmljYW5hIGZyZW50ZSBhIHBhcnF1ZSBTYW4gTWFydMOtbiwgU2FudGEgVGVjbGEsIEVsIFNhbHZhZG9yWkwiSmNhcnJldGVyYSBwYW5hbWVyaWNhbmEgZnJlbnRlIGEgcGFycXVlIHNhbiBtYXJ0w61uIHNhbnRhIHRlY2xhIGVsIHNhbHZhZG9ykgENcGl6emF0YWtlYXdheZoBRENpOURRVWxSUVVOdlpFTm9kSGxqUmpsdlQya3hlVnByVG1sa01HUkVVVEpLVWt4VlJYaGxWMFY2WWtkU05WVnNSUkFC4AEA-gEECAAQRw!16s%2Fg%2F11b7fx99x1?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@13.709226,-89.2096818,3a,75y,123.14h,75.42t/data=!3m7!1e1!3m5!1sCIABIhA3d6BkvbwT01HPT_Ww_h_N!2e10!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53tEl2JenjfIDyyIVRAbJ5ryP9wHOSYyoTGjd8wbzOrhaWijOSIPL-vsP-85OE30eqs-JQZ9C-5VVTF5gWV41Iyn-IqkpYezIhXal0Ik5PhLwuolBxN6ipxNJKIfr88gDP1JUjCebJ0mmXk%3Dw900-h600-k-no-pi14.583557912263586-ya43.47784003517276-ro0-fo100!7i7680!8i3840?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Quiznos+Los+H%C3%A9roes/@13.709179,-89.2096717,21z/data=!4m14!1m7!3m6!1s0x8f633061e9135787:0xc27f06b65bcf131b!2sQuiznos+Los+H%C3%A9roes!8m2!3d13.7091279!4d-89.2095352!16s%2Fg%2F1tfg8q_q!3m5!1s0x8f633061e9135787:0xc27f06b65bcf131b!8m2!3d13.7091279!4d-89.2095352!16s%2Fg%2F1tfg8q_q?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Farmacias+Econ%C3%B3micas+-+5ta+Avenida+Norte/@13.7141214,-89.1929109,20z/data=!4m14!1m7!3m6!1s0x8f63305dd9012333:0x33aceb7ce88e90fb!2sCentro+Nacional+de+Registros!8m2!3d13.7025315!4d-89.2136102!16s%2Fg%2F1thxx8fy!3m5!1s0x8f63311660b34c09:0x60c2016506f48b0d!8m2!3d13.7142659!4d-89.1927797!16s%2Fg%2F11gjhfpkkm?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@13.7142776,-89.1926344,3a,75y,232.2h,85.93t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgICb_uKk9wE!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53wOvXyS5GM1ToAvPBkGzbdEjzD6kHrdPpUsCZoW0NncmdOxYyI5f1Qn2n89qtEcRfSoCLTetlTgp1kYQeEQ4TjX-8w5isQs98Dwac9egDPUxKCADezwxLmCNQK9SSb-RxLO0AESA%3Dw900-h600-k-no-pi4.067694391504801-ya219.68225532953403-ro0-fo100!7i8000!8i4000?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Santa Helena</t>
+  </si>
+  <si>
+    <t>La Campana</t>
+  </si>
+  <si>
+    <t>Parque San Martin</t>
+  </si>
+  <si>
+    <t>Centro Nacional Registros</t>
+  </si>
+  <si>
+    <t>CC Las Acacias</t>
+  </si>
+  <si>
+    <t>Plaza Orion</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Taquer%C3%ADa+Los+H%C3%A9roes+503+%7C+Sucursal+San+Luis/@13.7153452,-89.2125365,3a,75y,210.79h,92.25t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgIDjmaWRJg!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf508uBZbbaqxlWroNLjITDIGhSirmX5JBd_PdmH8ZW0pIalnjG2fQ2O3mPIM4T_7jPFp50K9GlXGgaZIw8xNm119dTxs3bkeGHlmbCwoWCBU2zZ1Yn6POR5nF4LyGh9DsKZzgEg%3Dw900-h600-k-no-pi-2.245010472316835-ya284.9377635013032-ro0-fo100!7i8000!8i4000!4m14!1m7!3m6!1s0x8f633b3ffc44c6ed:0xedd0a0ac751bb5ac!2sTaquer%C3%ADa+Los+H%C3%A9roes+503+%7C+Sucursal+San+Luis!8m2!3d13.715139!4d-89.2116457!16s%2Fg%2F11l1qcycgf!3m5!1s0x8f633b3ffc44c6ed:0xedd0a0ac751bb5ac!8m2!3d13.715139!4d-89.2116457!16s%2Fg%2F11l1qcycgf?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Farmacias+Econ%C3%B3micas+-+San+Luis/@13.7153419,-89.2128474,21z/data=!4m6!3m5!1s0x8f6331f9ba44afe3:0x4790890dc4bd27e7!8m2!3d13.7152564!4d-89.2126609!16s%2Fg%2F11g18_3rr9?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Centro+Comercial+Las+Acacias/@13.6760503,-89.2267652,3a,90y,288.5h,72.67t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgICjv92p3AE!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf52wFK_td2n4mKpy3RA5a7x-xnnowYIUl7yWmj9VzdPYVUJMsPjNoMubqM3a1eTDxa4kT4yf-f_TRYMCIjIeNNCFEtohpKZ8j_8DsOxy7HCcyXUh2rG0vh-IBdsnZXnaysiRFdo16g%3Dw900-h600-k-no-pi17.32746333636844-ya79.51447852852348-ro0-fo100!7i8000!8i4000!4m14!1m7!3m6!1s0x8f6331b5e671cef7:0x6d1c1ba608a84089!2sCentro+Comercial+Las+Acacias!8m2!3d13.6762059!4d-89.2270071!16s%2Fg%2F11c0rqvxh4!3m5!1s0x8f6331b5e671cef7:0x6d1c1ba608a84089!8m2!3d13.6762059!4d-89.2270071!16s%2Fg%2F11c0rqvxh4?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/El+Chory/@13.7023881,-89.2356003,3a,75y,4.69h,85.8t/data=!3m8!1e1!3m6!1sCIABIhD_6K9AYdln3eIZSGU3ON7i!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf50dQDt1IBW4hFckjYA2X4Rf1vz8bAve-oWhMDEHb9gRT8toPahbdW1NVZWF-bK2tj30BHNoAcFCq8AhH02-1mo_5SyAxm31QFfWkl9S179Ej6tKZ3tlLm7m48Y_C-ExrMWdPRe3etGrXS0n%3Dw900-h600-k-no-pi4.200426584331552-ya205.4262768591492-ro0-fo100!7i7680!8i3840!4m15!1m8!3m7!1s0x8f63303d101d661f:0x7db010d52f2bcc07!2sP.%C2%BA+Gral.+Escal%C3%B3n+4018,+San+Salvador!3b1!8m2!3d13.7026237!4d-89.2354067!16s%2Fg%2F11h6df108t!3m5!1s0x8f63316161beeef3:0xa3b2dc9c44966776!8m2!3d13.7024539!4d-89.235608!16s%2Fg%2F11v5wc6ddn?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bocadillos+Taiwaneses+Uncle+Yang/@13.7024792,-89.2358567,21z/data=!4m15!1m8!3m7!1s0x8f63303d101d661f:0x7db010d52f2bcc07!2sP.%C2%BA+Gral.+Escal%C3%B3n+4018,+San+Salvador!3b1!8m2!3d13.7026237!4d-89.2354067!16s%2Fg%2F11h6df108t!3m5!1s0x8f63303d10b28ddd:0xaf4fbc2d5c3e675!8m2!3d13.7026354!4d-89.2356593!16s%2Fg%2F11b8v9jzdg?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Quiznos los Heroes</t>
+  </si>
+  <si>
+    <t>Farmacias Uno - San Luis</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Parada+Salandra/@13.6996202,-89.1895104,3a,75y,340.33h,86.64t/data=!3m7!1e1!3m5!1sCIHM0ogKEICAgIDT166vkwE!2e10!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53E5OsGexSzZT9jNuePgb-J43InUELDuf2rf5ZLyiIL9ylNYOvkIPaAhydYN4Md0s3A1IDWKJT0WGV2QaHwlWyjao42SCBwEQsW6CJNrj8gbKwwt130xbpzNxhtW7zF_-xEkRxPuw%3Dw900-h600-k-no-pi3.360142351383729-ya67.13524219325672-ro0-fo100!7i8000!8i4000!4m14!1m7!3m6!1s0x8f6330ea1449336b:0xb403b4c9c1bf71db!2sBAC+Credomatic+%7C+Centro!8m2!3d13.6998094!4d-89.1905811!16s%2Fg%2F11f13g5ldd!3m5!1s0x8f6330ebb60115cf:0xf259a3590bff6bdd!8m2!3d13.6996954!4d-89.1895169!16s%2Fg%2F1hjh1rkpm?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Go+Green+%E2%80%A2+Zona+Rosa/@13.6923317,-89.2367781,3a,75y,79.17h,94.92t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgICj1d3oDw!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf50c1HRzeuLj1aG-dW4rsq1P-aSGDEtj3tMWXKyDI--sysc3RwRUuWq2zwas8ghkF1JRb324B1iNvaYBxqwUjdM-n42bJyMxDJh7pop3m3IF6nL5Ovb2CIUTilX7L76uQayhZR7z%3Dw900-h600-k-no-pi-4.9179827012792-ya51.6081036865242-ro0-fo100!7i8000!8i4000!4m14!1m7!3m6!1s0x8f6331de43ef2545:0x6c79c2bc57d5e886!2sGo+Green+%E2%80%A2+Zona+Rosa!8m2!3d13.6923332!4d-89.2365829!16s%2Fg%2F11h1vbr71z!3m5!1s0x8f6331de43ef2545:0x6c79c2bc57d5e886!8m2!3d13.6923332!4d-89.2365829!16s%2Fg%2F11h1vbr71z?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@13.7001356,-89.1526645,3a,81.7y,177.63h,90.03t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgIDT9v7MLw!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf51vPWnx9sIcTPD5gVxjtkoOtsjUUQW0Ll2lobdK3yOK20uh-rWeK_sDxbFwSZLcvmj0Ya1uisss8_QodsvU0M143XXMEDy2QQsfTFy_XcIWXYSl07VgwGJa6ZE00qazlx2Y1hZl%3Dw900-h600-k-no-pi-0.030000000000001137-ya73.3706768798828-ro0-fo100!7i8000!8i4000?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/AMPM+%7C+Pr%C3%B3ceres/@13.6834361,-89.2325123,3a,75y,341.02h,103.11t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgIDZqJSeIg!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf50PCvBdVcypbQVbRrdvGzToBe7ickExbrkFstg8X51qvupDoRW0EqpFz8TKVxrlk9FrAWKIi8ZFpNAbk57timNCzOXaH2UwfZi1FbLpEFgNmhVYKWhiz97k-mgDROeCyt2pWqYQ%3Dw900-h600-k-no-pi-13.112573020442483-ya56.59953890692543-ro0-fo100!7i3840!8i1920!4m6!3m5!1s0x8f6331de7707d09f:0x885eaa64c0c7c072!8m2!3d13.6836075!4d-89.2325571!16s%2Fg%2F11tn25694_?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/AMPM+%7C+Tuscania/@13.619467,-89.2847614,3a,80.9y,260.26h,89.12t/data=!3m8!1e1!3m6!1sCIABIhB7NiqzfBwY7nrPzOD8nTGW!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53m18UWLkgJ-30lVabxMonHe6BEGp7OQ0ICudUdarR1_gvSdXI-_uFX0IeEHbJSVSu-_hUCKv4F3NYDGhdlW6HEYSCVgJ0mZ5mHAqW8EZSf7tfQmbkOW_c3JH4KTcig4SW2REMyHNH0BSol%3Dw900-h600-k-no-pi0.8801786610429048-ya41.57500231460827-ro0-fo100!7i7680!8i3840!4m6!3m5!1s0x8f632d444885dacf:0x8e33b6119eba1607!8m2!3d13.6191645!4d-89.2861703!16s%2Fg%2F11v0hhf20b?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/AMPM+%7C+Masferrer/@13.7077467,-89.2488194,3a,75y,91.95h,100.84t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgICj8s-5Gw!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53dQUiTIRDE0TwAWcyH-Ih8DyyUbmh7wHgumDWEyhRpIy3WAgH-xnZQMvsqiRFKFKnR1FQXlYJNuHbOzU0U5Y-Hg1TniozyV04E1oI4PnDHvCY7w8465mHXmhYlvOZdRkd4O0g%3Dw900-h600-k-no-pi-10.84029827546108-ya255.7537697452363-ro0-fo100!7i8000!8i4000!4m6!3m5!1s0x8f632fc9b980c41f:0xa3fd3467b7ccf1dc!8m2!3d13.707683!4d-89.2485359!16s%2Fg%2F11v0hhhr2x?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>AMPM01 - Proceres</t>
+  </si>
+  <si>
+    <t>AMPM02 - Tuscania</t>
+  </si>
+  <si>
+    <t>AMPM03 - Masferrer</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1XKR9p1Mv4kJ_3TKokNbUW5BiyRX4bPjr/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cfMguNc2wW3Z7SaS6VGgydYhvpMrxX1v/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14Z9l2wF5VkmVSnHVJHNhDUIcsiC3UHFI/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1j0SijLMBdejHwvZNeofYU3qp-29euJaD/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1yPmrJdHkMG1Wtbbqq4fn74vzt1LBAq5H/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1V8cr4c1LgDMq6ElLo0dlOPwRk3irOS4e/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_cuuVcjVDcaVm06DT7KX8VEKskISwQhe/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fsOhYVoKuPle26JcHriZvAG6Kk_HgOob/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1D1O_QjxnG0RyY8D6W3Nf3BgwqntCfPeV/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1PzYfpE8FCSm6h_MFie9dCBs7UVbLH8l5/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YmixwCsPak8D1ny5t0tjURjV8KM_L9d8/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1qQpqbYTpe4SBYXeStFVQDZkfEss5Ytoi/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1H6gViIY9gfgTeTk_GQhD69B5vLhMkPXd/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZB3XivelA15lrUtroIiTY1mveZwj4bB7/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,6 +296,14 @@
       <b/>
       <sz val="9"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -315,7 +359,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -344,15 +388,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -392,10 +427,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -409,34 +445,28 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -444,8 +474,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -764,386 +796,412 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F46DCDA-C7C3-4424-BB31-50D911829D44}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="3" max="3" width="51.21875" style="16" customWidth="1"/>
+    <col min="3" max="3" width="51.21875" style="14" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="85.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.88671875" customWidth="1"/>
+    <col min="7" max="7" width="40.88671875" customWidth="1"/>
     <col min="9" max="9" width="3.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="11"/>
+        <v>6</v>
+      </c>
+      <c r="C1" s="10"/>
       <c r="I1" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="C2" s="11"/>
       <c r="I2" t="s">
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
+        <v>4</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
       <c r="I3" t="s">
         <v>2</v>
       </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>50</v>
+      <c r="E4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>33</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="17">
-        <v>6.89</v>
+        <v>61</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="15">
+        <v>6.3470000000000004</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="G5" t="s">
+        <v>58</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="17">
+      <c r="B6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="15">
         <v>7.1</v>
       </c>
-      <c r="F6" t="s">
-        <v>64</v>
+      <c r="F6" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="17">
+      <c r="B7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="15">
         <v>6.56</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="G7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="17">
-        <v>6.69</v>
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="15">
+        <v>6.86</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>67</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="17" t="s">
+      <c r="B9" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="17">
-        <v>5.84</v>
+      <c r="C9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="15">
+        <v>5.9</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>68</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="17">
-        <v>6.67</v>
+      <c r="E10" s="15">
+        <v>6.42</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>69</v>
+      </c>
+      <c r="G10" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="17">
+      <c r="B11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="15">
         <v>5.72</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>70</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="17">
-        <v>5.58</v>
+        <v>8</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="15">
+        <v>5.63</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>77</v>
+      </c>
+      <c r="G12" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="17">
-        <v>6.13</v>
+        <v>8</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="15">
+        <v>6.23</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="G13" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="17">
+      <c r="B14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="15">
         <v>6.53</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="17">
-        <v>6.84</v>
+      <c r="B15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="15">
+        <v>6.81</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>73</v>
+      </c>
+      <c r="G15" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="17">
-        <v>5.1100000000000003</v>
+        <v>8</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="15">
+        <v>5.13</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="17">
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="15">
         <v>6.58</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="17">
-        <v>5.86</v>
+        <v>75</v>
+      </c>
+      <c r="G17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="15">
+        <v>6.2</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" s="17">
-        <v>6.27</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
+        <v>76</v>
+      </c>
+      <c r="G18" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Cubo_Sitelo.xlsx
+++ b/Cubo_Sitelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerald Rocha\Documents\GitHub\Mapa TN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3648E3E0-7A0C-4C5C-A22E-F472ED2D553F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE63207D-36C7-4FD2-8257-4F479E29DFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B2C8BF5B-C28F-4A4B-B360-42E661C3BE08}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
   <si>
     <t>PC</t>
   </si>
@@ -262,13 +262,25 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1ZB3XivelA15lrUtroIiTY1mveZwj4bB7/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@13.6673515,-89.2708628,3a,75y,189.07h,87.22t/data=!3m7!1e1!3m5!1sCIABIhDYnU-8QaaSt8N_pvIfAOAj!2e10!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf51rcNe9Q79vFaoQ8egNbbErXLs9yQ-LRH_H6KYoprQ2_l6EIJZ45KFbz4ghNu2hczTstSauhhM8gT8tfQtCKKVjpwaPzkhpMEmWwX0sMF4ejXMWLJIAH1Q0GVBaT8TvAO-Z4yioK7gMZD-T%3Dw900-h600-k-no-pi2.78080123246653-ya73.94424301043091-ro0-fo100!7i7680!8i3840?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Plaza+Malta/@13.6670866,-89.2727685,17z/data=!3m1!4b1!4m6!3m5!1s0x8f632e45d539703d:0x91871f581bcc45c4!8m2!3d13.6670814!4d-89.2701882!16s%2Fg%2F11fxb7zzvg?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Plaza Malta antiguo Cuscatlan</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1oBrZI3euHoPAyGJYPYVloDASA6opPGLC/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,14 +308,6 @@
       <b/>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -427,11 +431,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -474,10 +477,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -796,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F46DCDA-C7C3-4424-BB31-50D911829D44}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -921,7 +922,7 @@
       <c r="E6" s="15">
         <v>7.1</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" t="s">
         <v>65</v>
       </c>
       <c r="G6" t="s">
@@ -1181,7 +1182,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1202,6 +1203,29 @@
       </c>
       <c r="G18" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="15">
+        <v>6.62</v>
+      </c>
+      <c r="F19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/Cubo_Sitelo.xlsx
+++ b/Cubo_Sitelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerald Rocha\Documents\GitHub\Mapa TN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE63207D-36C7-4FD2-8257-4F479E29DFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7BC40A-2065-4A5D-B31D-DA8A7AEEEE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B2C8BF5B-C28F-4A4B-B360-42E661C3BE08}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$4:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
   <si>
     <t>PC</t>
   </si>
@@ -126,9 +126,6 @@
     <t>Link PDF Sitelo</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/Restaurante+Kreef+%E2%80%A2+Santa+Elena/@13.6680113,-89.2564638,3a,75y,133.17h,97.82t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgICx3Ze-TA!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53ahnY0LpyIi0bKPdnJo9epDs25_23h4wz7q3PVyHmpj9MkrZiskHCkQDmgNVTzM9ACecXxMY1WVewhOoFgM2DS2agZpC_5e5dMT0z7FLK5w9rEAFZw1bnWD540wsbfDCiL-mdF%3Dw900-h600-k-no-pi-7.824501826098839-ya76.81318855877765-ro0-fo100!7i3840!8i1920!4m10!1m2!2m1!1sBulevar+Santa+Elena+San+Salvador+CP,+1101,+El+Salvador!3m6!1s0x8f632e2fec9a41f7:0x624adb154d2cfc6d!8m2!3d13.6713362!4d-89.2549542!10e5!16s%2Fg%2F1hc3bkwx6?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
     <t>Link Street View</t>
   </si>
   <si>
@@ -156,9 +153,6 @@
     <t>https://www.google.com/maps/@13.7142776,-89.1926344,3a,75y,232.2h,85.93t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgICb_uKk9wE!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53wOvXyS5GM1ToAvPBkGzbdEjzD6kHrdPpUsCZoW0NncmdOxYyI5f1Qn2n89qtEcRfSoCLTetlTgp1kYQeEQ4TjX-8w5isQs98Dwac9egDPUxKCADezwxLmCNQK9SSb-RxLO0AESA%3Dw900-h600-k-no-pi4.067694391504801-ya219.68225532953403-ro0-fo100!7i8000!8i4000?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
   <si>
-    <t>Santa Helena</t>
-  </si>
-  <si>
     <t>La Campana</t>
   </si>
   <si>
@@ -195,9 +189,6 @@
     <t>Farmacias Uno - San Luis</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/Parada+Salandra/@13.6996202,-89.1895104,3a,75y,340.33h,86.64t/data=!3m7!1e1!3m5!1sCIHM0ogKEICAgIDT166vkwE!2e10!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53E5OsGexSzZT9jNuePgb-J43InUELDuf2rf5ZLyiIL9ylNYOvkIPaAhydYN4Md0s3A1IDWKJT0WGV2QaHwlWyjao42SCBwEQsW6CJNrj8gbKwwt130xbpzNxhtW7zF_-xEkRxPuw%3Dw900-h600-k-no-pi3.360142351383729-ya67.13524219325672-ro0-fo100!7i8000!8i4000!4m14!1m7!3m6!1s0x8f6330ea1449336b:0xb403b4c9c1bf71db!2sBAC+Credomatic+%7C+Centro!8m2!3d13.6998094!4d-89.1905811!16s%2Fg%2F11f13g5ldd!3m5!1s0x8f6330ebb60115cf:0xf259a3590bff6bdd!8m2!3d13.6996954!4d-89.1895169!16s%2Fg%2F1hjh1rkpm?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/place/Go+Green+%E2%80%A2+Zona+Rosa/@13.6923317,-89.2367781,3a,75y,79.17h,94.92t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgICj1d3oDw!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf50c1HRzeuLj1aG-dW4rsq1P-aSGDEtj3tMWXKyDI--sysc3RwRUuWq2zwas8ghkF1JRb324B1iNvaYBxqwUjdM-n42bJyMxDJh7pop3m3IF6nL5Ovb2CIUTilX7L76uQayhZR7z%3Dw900-h600-k-no-pi-4.9179827012792-ya51.6081036865242-ro0-fo100!7i8000!8i4000!4m14!1m7!3m6!1s0x8f6331de43ef2545:0x6c79c2bc57d5e886!2sGo+Green+%E2%80%A2+Zona+Rosa!8m2!3d13.6923332!4d-89.2365829!16s%2Fg%2F11h1vbr71z!3m5!1s0x8f6331de43ef2545:0x6c79c2bc57d5e886!8m2!3d13.6923332!4d-89.2365829!16s%2Fg%2F11h1vbr71z?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
   <si>
@@ -207,9 +198,6 @@
     <t>https://www.google.com/maps/place/AMPM+%7C+Pr%C3%B3ceres/@13.6834361,-89.2325123,3a,75y,341.02h,103.11t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgIDZqJSeIg!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf50PCvBdVcypbQVbRrdvGzToBe7ickExbrkFstg8X51qvupDoRW0EqpFz8TKVxrlk9FrAWKIi8ZFpNAbk57timNCzOXaH2UwfZi1FbLpEFgNmhVYKWhiz97k-mgDROeCyt2pWqYQ%3Dw900-h600-k-no-pi-13.112573020442483-ya56.59953890692543-ro0-fo100!7i3840!8i1920!4m6!3m5!1s0x8f6331de7707d09f:0x885eaa64c0c7c072!8m2!3d13.6836075!4d-89.2325571!16s%2Fg%2F11tn25694_?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/AMPM+%7C+Tuscania/@13.619467,-89.2847614,3a,80.9y,260.26h,89.12t/data=!3m8!1e1!3m6!1sCIABIhB7NiqzfBwY7nrPzOD8nTGW!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53m18UWLkgJ-30lVabxMonHe6BEGp7OQ0ICudUdarR1_gvSdXI-_uFX0IeEHbJSVSu-_hUCKv4F3NYDGhdlW6HEYSCVgJ0mZ5mHAqW8EZSf7tfQmbkOW_c3JH4KTcig4SW2REMyHNH0BSol%3Dw900-h600-k-no-pi0.8801786610429048-ya41.57500231460827-ro0-fo100!7i7680!8i3840!4m6!3m5!1s0x8f632d444885dacf:0x8e33b6119eba1607!8m2!3d13.6191645!4d-89.2861703!16s%2Fg%2F11v0hhf20b?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/place/AMPM+%7C+Masferrer/@13.7077467,-89.2488194,3a,75y,91.95h,100.84t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgICj8s-5Gw!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53dQUiTIRDE0TwAWcyH-Ih8DyyUbmh7wHgumDWEyhRpIy3WAgH-xnZQMvsqiRFKFKnR1FQXlYJNuHbOzU0U5Y-Hg1TniozyV04E1oI4PnDHvCY7w8465mHXmhYlvOZdRkd4O0g%3Dw900-h600-k-no-pi-10.84029827546108-ya255.7537697452363-ro0-fo100!7i8000!8i4000!4m6!3m5!1s0x8f632fc9b980c41f:0xa3fd3467b7ccf1dc!8m2!3d13.707683!4d-89.2485359!16s%2Fg%2F11v0hhhr2x?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
   <si>
@@ -264,9 +252,6 @@
     <t>https://drive.google.com/file/d/1ZB3XivelA15lrUtroIiTY1mveZwj4bB7/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/@13.6673515,-89.2708628,3a,75y,189.07h,87.22t/data=!3m7!1e1!3m5!1sCIABIhDYnU-8QaaSt8N_pvIfAOAj!2e10!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf51rcNe9Q79vFaoQ8egNbbErXLs9yQ-LRH_H6KYoprQ2_l6EIJZ45KFbz4ghNu2hczTstSauhhM8gT8tfQtCKKVjpwaPzkhpMEmWwX0sMF4ejXMWLJIAH1Q0GVBaT8TvAO-Z4yioK7gMZD-T%3Dw900-h600-k-no-pi2.78080123246653-ya73.94424301043091-ro0-fo100!7i7680!8i3840?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/place/Plaza+Malta/@13.6670866,-89.2727685,17z/data=!3m1!4b1!4m6!3m5!1s0x8f632e45d539703d:0x91871f581bcc45c4!8m2!3d13.6670814!4d-89.2701882!16s%2Fg%2F11fxb7zzvg?entry=ttu&amp;g_ep=EgoyMDI2MDUxMC4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
   <si>
@@ -274,6 +259,24 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1oBrZI3euHoPAyGJYPYVloDASA6opPGLC/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@13.6673262,-89.2707974,3a,75y,176.89h,103.22t/data=!3m7!1e1!3m5!1sCIHM0ogKEICAgIDj3oySSw!2e10!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53Nypz4ilosmG7m3Br8IKipJc7ZKG_0ofdysGEm-QeEogbFu4-8u4IbeVldJBhl-lApJoBDSoNH2Rev78QdrCa5tHVI_pmMdJQcBoWGO4EhNPISmBMFyPRLWdAxdMBlK8w7vkG7%3Dw900-h600-k-no-pi-13.220551478104198-ya81.42679433284698-ro0-fo100!7i8000!8i4000?entry=ttu&amp;g_ep=EgoyMDI2MDUxMi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Santa Elena</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@13.6680926,-89.2564237,3a,75y,140.66h,89.6t/data=!3m8!1e1!3m6!1sCIHM0ogKEICAgICx3ZfimAE!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf53cTsCr6OK8zWlnd-_exH6MlL3IyPslU5OPRiAq9rde1nwoAsuIqJwleB0DsMmQvfCUxxmwIsVmP8nVb-cfpkZu-7r6yMMoBmJXcZP2g2-ZxWvPYd_m6iRxt2WjfP1L9mcBxVlszQ%3Dw900-h600-k-no-pi0.40250027264377763-ya83.93063637975837-ro0-fo100!7i3840!8i1920?entry=ttu&amp;g_ep=EgoyMDI2MDUxMi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Prioridad TN</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@13.6996354,-89.1897533,3a,75y,71.78h,81.87t/data=!3m7!1e1!3m5!1sCIHM0ogKEICAgICn4c7NRw!2e10!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf507LgW6tubU51gT4JIEIt8DO0rtZ-Bn5sbgw6M8bEFGuGbAqZyXGedoL_5IPfLmqIwH5Dt8n7biKBMmDV0fVnRPhfILRW9eMgJxnqmLQcgAZrDLX8xGz6DCQf6Qmy3mEUrh3CoR%3Dw900-h600-k-no-pi8.131442822415963-ya320.8949544474734-ro0-fo100!7i8000!8i4000?entry=ttu&amp;g_ep=EgoyMDI2MDUxMy4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@13.6195565,-89.2847476,3a,75y,268.39h,80.35t/data=!3m8!1e1!3m6!1sCIABIhAadytJv78SKDxvQf3COv8h!2e10!3e11!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FABJJf518qXrqiXvnlAjCOdLPPpxSpV8rR3LYVAXVl6j6Vi_hWwEQP6y_vw-a0DAVURC5qCHpmoPp_xA-1_QvZlWlQypVQsBcFbsUsRiL8btlGygTDhibwXvJ1MJU5cxdbfUBXOW_WrqF10X4FJzN%3Dw900-h600-k-no-pi9.648064329837524-ya50.201179006098016-ro0-fo100!7i7680!8i3840?entry=ttu&amp;g_ep=EgoyMDI2MDUxMy4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -434,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -477,6 +480,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -797,58 +801,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F46DCDA-C7C3-4424-BB31-50D911829D44}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="3" max="3" width="51.21875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
+    <col min="3" max="3" width="30.77734375" style="14" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.88671875" customWidth="1"/>
-    <col min="7" max="7" width="40.88671875" customWidth="1"/>
-    <col min="9" max="9" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.88671875" customWidth="1"/>
+    <col min="8" max="8" width="40.88671875" customWidth="1"/>
+    <col min="10" max="10" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="10"/>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="11"/>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
-      <c r="I3" t="s">
+      <c r="F3" s="13"/>
+      <c r="J3" t="s">
         <v>2</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -865,24 +871,27 @@
         <v>25</v>
       </c>
       <c r="F4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="H4" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>14</v>
@@ -893,25 +902,28 @@
       <c r="E5" s="15">
         <v>6.3470000000000004</v>
       </c>
-      <c r="F5" t="s">
-        <v>64</v>
+      <c r="F5" s="15">
+        <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" t="s">
         <v>8</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>15</v>
@@ -922,19 +934,22 @@
       <c r="E6" s="15">
         <v>7.1</v>
       </c>
-      <c r="F6" t="s">
-        <v>65</v>
+      <c r="F6" s="15">
+        <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>16</v>
@@ -945,22 +960,25 @@
       <c r="E7" s="15">
         <v>6.56</v>
       </c>
-      <c r="F7" t="s">
-        <v>66</v>
+      <c r="F7" s="15">
+        <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="H7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>24</v>
@@ -968,22 +986,25 @@
       <c r="E8" s="15">
         <v>6.86</v>
       </c>
-      <c r="F8" t="s">
-        <v>67</v>
+      <c r="F8" s="15">
+        <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+      <c r="H8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>24</v>
@@ -991,22 +1012,25 @@
       <c r="E9" s="15">
         <v>5.9</v>
       </c>
-      <c r="F9" t="s">
-        <v>68</v>
+      <c r="F9" s="15">
+        <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+      <c r="H9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>24</v>
@@ -1014,19 +1038,22 @@
       <c r="E10" s="15">
         <v>6.42</v>
       </c>
-      <c r="F10" t="s">
-        <v>69</v>
+      <c r="F10" s="15">
+        <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+      <c r="H10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>11</v>
@@ -1037,22 +1064,25 @@
       <c r="E11" s="15">
         <v>5.72</v>
       </c>
-      <c r="F11" t="s">
-        <v>70</v>
+      <c r="F11" s="15">
+        <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>24</v>
@@ -1060,22 +1090,25 @@
       <c r="E12" s="15">
         <v>5.63</v>
       </c>
-      <c r="F12" t="s">
-        <v>77</v>
+      <c r="F12" s="15">
+        <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+      <c r="H12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>24</v>
@@ -1083,19 +1116,22 @@
       <c r="E13" s="15">
         <v>6.23</v>
       </c>
-      <c r="F13" t="s">
-        <v>71</v>
+      <c r="F13" s="15">
+        <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>12</v>
@@ -1106,22 +1142,25 @@
       <c r="E14" s="15">
         <v>6.53</v>
       </c>
-      <c r="F14" t="s">
-        <v>72</v>
+      <c r="F14" s="15">
+        <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+      <c r="H14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>24</v>
@@ -1129,14 +1168,17 @@
       <c r="E15" s="15">
         <v>6.81</v>
       </c>
-      <c r="F15" t="s">
-        <v>73</v>
+      <c r="F15" s="15">
+        <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="H15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -1152,14 +1194,17 @@
       <c r="E16" s="15">
         <v>5.13</v>
       </c>
-      <c r="F16" t="s">
-        <v>74</v>
+      <c r="F16" s="15">
+        <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="H16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -1175,14 +1220,17 @@
       <c r="E17" s="15">
         <v>6.58</v>
       </c>
-      <c r="F17" t="s">
-        <v>75</v>
+      <c r="F17" s="15">
+        <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+      <c r="H17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1198,22 +1246,25 @@
       <c r="E18" s="15">
         <v>6.2</v>
       </c>
-      <c r="F18" t="s">
-        <v>76</v>
+      <c r="F18" s="15">
+        <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="H18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>24</v>
@@ -1221,14 +1272,20 @@
       <c r="E19" s="15">
         <v>6.62</v>
       </c>
-      <c r="F19" t="s">
-        <v>81</v>
+      <c r="F19" s="15">
+        <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C8" r:id="rId1" xr:uid="{027CA563-8D4B-4637-9621-DCF664D294AA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>